--- a/equipcaldeira1-INPASA.xlsx
+++ b/equipcaldeira1-INPASA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\CALDEIRA 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCFC4B4-8B99-4AB6-953D-7CFF7A87D3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D81C64A-3459-4573-BB14-3FFA3C230427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
   <si>
     <t>TAG</t>
   </si>
@@ -187,6 +187,9 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/LP1041013825141.pdf</t>
+  </si>
+  <si>
+    <t>EM EQUIPAMENTO SENDO DESMONTADO</t>
   </si>
 </sst>
 </file>
@@ -286,11 +289,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -450,10 +453,12 @@
     <sheetNames>
       <sheetName val="Equipamentos"/>
       <sheetName val="Instrucoes"/>
+      <sheetName val="equipcaldeira1-INPASA"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -655,7 +660,7 @@
     <col min="10" max="10" width="13.5" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.75" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.125" style="2" customWidth="1"/>
     <col min="14" max="14" width="11.75" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" style="2" customWidth="1"/>
     <col min="16" max="16" width="10.625" style="2" customWidth="1"/>
@@ -720,7 +725,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="9" customFormat="1" ht="57">
+    <row r="2" spans="1:18" s="8" customFormat="1" ht="57">
       <c r="A2" s="4" t="s">
         <v>42</v>
       </c>
@@ -764,9 +769,11 @@
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-    </row>
-    <row r="3" spans="1:18" s="9" customFormat="1" ht="57">
+      <c r="Q2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="8" customFormat="1" ht="57">
       <c r="A3" s="4" t="s">
         <v>47</v>
       </c>
@@ -810,7 +817,9 @@
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
+      <c r="Q3" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="24" customHeight="1">
       <c r="A4" s="3"/>
@@ -2074,14 +2083,14 @@
   <conditionalFormatting sqref="R1">
     <cfRule type="duplicateValues" dxfId="2" priority="15"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R3">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R4:R69">
-    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -2098,10 +2107,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">

--- a/equipcaldeira1-INPASA.xlsx
+++ b/equipcaldeira1-INPASA.xlsx
@@ -5,20 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\CALDEIRA 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\PAGINAS WEB\DATABOOK_INPASA\CALDEIRA 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D81C64A-3459-4573-BB14-3FFA3C230427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195BB12F-D7D2-4356-B3C0-C9A6CFE1EB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucoes" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="127">
   <si>
     <t>TAG</t>
   </si>
@@ -87,9 +84,6 @@
     <t>Fotos_Adicionais</t>
   </si>
   <si>
-    <t>Observacoes</t>
-  </si>
-  <si>
     <t>INSTRUÇÕES DE USO</t>
   </si>
   <si>
@@ -162,9 +156,6 @@
     <t xml:space="preserve"> assets/pdf/manualcoaxial.pdf</t>
   </si>
   <si>
-    <t>TAG Nº</t>
-  </si>
-  <si>
     <t>RELATORIO FINAL</t>
   </si>
   <si>
@@ -174,22 +165,316 @@
     <t>C62344NA00GAW</t>
   </si>
   <si>
-    <t>*****MOTOR 5 CV 4 POLOS</t>
-  </si>
-  <si>
     <t>5,3 L</t>
   </si>
   <si>
-    <t xml:space="preserve"> assets/pdf/LP401012825139.pdf</t>
-  </si>
-  <si>
     <t>RE-401013</t>
   </si>
   <si>
-    <t xml:space="preserve"> assets/pdf/LP1041013825141.pdf</t>
-  </si>
-  <si>
-    <t>EM EQUIPAMENTO SENDO DESMONTADO</t>
+    <t xml:space="preserve"> assets/pdf/LP V56344NK00DAW - 834164.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LP V58341NK00FAW  - 401048 - 822892.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LP V58341NK00FAW - 822891.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LP V58341NK00FAW - 822893.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LP V58341NK00FAW - 822897.pdf</t>
+  </si>
+  <si>
+    <t>MOTOREDUTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/manualvertimax.pdf</t>
+  </si>
+  <si>
+    <t>RE-401048</t>
+  </si>
+  <si>
+    <t>RE-401089</t>
+  </si>
+  <si>
+    <t>OS 6329
+TAG 7596336
+TAG MOTOR 7596339
+OS MOTOR</t>
+  </si>
+  <si>
+    <t>OS 6317
+TAG 7597102
+TAG MOTOR 7596360
+OS MOTOR 6319</t>
+  </si>
+  <si>
+    <t>OS 6325
+TAG 7597170
+TAG MOTOR 7597171
+OS MOTOR 6326</t>
+  </si>
+  <si>
+    <t>OS 6311
+TAG 7597128
+TAG MOTOR 7596325
+OS MOTOR 6312</t>
+  </si>
+  <si>
+    <t>OS 6320
+TAG 7596334
+TAG MOTOR 7597109
+OS MOTOR 6322</t>
+  </si>
+  <si>
+    <t>RE-401017B</t>
+  </si>
+  <si>
+    <t>RE-401057</t>
+  </si>
+  <si>
+    <t>RE-401056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OS 6333
+TAG 7596328
+TAG MOTOR 7597117
+OS MOTOR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OS 6331
+TAG 7596396
+TAG MOTOR 7596395
+OS MOTOR </t>
+  </si>
+  <si>
+    <t>RE-401088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OS 6327
+TAG 7596388
+TAG MOTOR 7596395
+OS MOTOR </t>
+  </si>
+  <si>
+    <t>RE-401050</t>
+  </si>
+  <si>
+    <t>OS 6314
+TAG 7596348
+TAG MOTOR 7596313
+OS MOTOR 6316</t>
+  </si>
+  <si>
+    <t>RE - 401049</t>
+  </si>
+  <si>
+    <t>V58341NK00FAW</t>
+  </si>
+  <si>
+    <t>MOTOR 3 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>OS 6309
+TAG 7597132
+TAG MOTOR 7597158
+OS MOTOR 6310</t>
+  </si>
+  <si>
+    <t>RE-401042B</t>
+  </si>
+  <si>
+    <t>OS 6341
+TAG 7596361
+TAG MOTOR 7597154
+OS MOTOR</t>
+  </si>
+  <si>
+    <t>OS 6342
+TAG 7597144
+TAG MOTOR 7596361
+OS MOTOR</t>
+  </si>
+  <si>
+    <t>OS 6345
+TAG 7596331
+TAG MOTOR 7596356
+OS MOTOR 6344</t>
+  </si>
+  <si>
+    <t>RE-401091</t>
+  </si>
+  <si>
+    <t>OS 6321
+TAG 7597145
+TAG MOTOR 7596329
+OS MOTOR</t>
+  </si>
+  <si>
+    <t>RE-401090</t>
+  </si>
+  <si>
+    <t>V56344NK00DPW</t>
+  </si>
+  <si>
+    <t>RE-401014</t>
+  </si>
+  <si>
+    <t>OS 6335
+TAG 7597135
+TAG MOTOR 7597156
+OS MOTOR 6336</t>
+  </si>
+  <si>
+    <t>3L</t>
+  </si>
+  <si>
+    <t>6.5L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6321.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6314.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6327.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6333.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6325.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6317.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6311.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6329.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6335.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6309.pdf</t>
+  </si>
+  <si>
+    <t>RE - 407056</t>
+  </si>
+  <si>
+    <t>OS 6337
+TAG 7597190
+TAG MOTOR 7596390
+OS MOTOR 6338</t>
+  </si>
+  <si>
+    <t>V56 - S/TAG 1</t>
+  </si>
+  <si>
+    <t>MOTOR 1 CV 4 POLOS MOD. 80</t>
+  </si>
+  <si>
+    <t>REDUTOR DUPLEX</t>
+  </si>
+  <si>
+    <t>ESPARGIDOR</t>
+  </si>
+  <si>
+    <t>RE-401014B</t>
+  </si>
+  <si>
+    <t>OS 6313 
+TAG 7596393
+TAG MOTOR 7597140
+OS MOTOR: 6315</t>
+  </si>
+  <si>
+    <t>MOTOR 5 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LP C62344NA00GAW.pdf</t>
+  </si>
+  <si>
+    <t>OS 6349
+TAG 7597157
+TAG MOTOR : 7596351
+OS MOTOR 6350</t>
+  </si>
+  <si>
+    <t>RE V58 S/TAG 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOTOR 1 CV 4 POLOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6331.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LP WCG20 F06 3 HH 80.pdf</t>
+  </si>
+  <si>
+    <t>2,7L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6349.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6345.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6342.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6320.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6341.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6337.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELAT - OS6313.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LP M0825223N1CAW1 - 401042 - 841338.pdf</t>
+  </si>
+  <si>
+    <t>F06</t>
+  </si>
+  <si>
+    <t>MOTOR 1,5 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>155.05</t>
+  </si>
+  <si>
+    <t>O,51KW</t>
+  </si>
+  <si>
+    <t>ISO VG 460 CLP PA0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/MAGMA M.pdf</t>
+  </si>
+  <si>
+    <t>TAG Nº2</t>
+  </si>
+  <si>
+    <t>OBSERVAÇOES</t>
+  </si>
+  <si>
+    <t>OS 6313 
+TAG 7596393
+TAG MOTOR 7597140
+OS MOTOR: 6315.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/img/vertimax.jpg</t>
   </si>
 </sst>
 </file>
@@ -218,7 +503,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,6 +538,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -266,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -292,6 +589,18 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -299,7 +608,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -444,50 +773,30 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Equipamentos"/>
-      <sheetName val="Instrucoes"/>
-      <sheetName val="equipcaldeira1-INPASA"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R69" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:R69" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R65" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
+  <autoFilter ref="A1:R65" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="21">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="OBSERVAÇOES" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº2" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -645,26 +954,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R69"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:R65"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.8984375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.09765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.59765625" style="2" customWidth="1"/>
     <col min="6" max="6" width="14" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.09765625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.19921875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.59765625" style="2" customWidth="1"/>
     <col min="10" max="10" width="13.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.69921875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.09765625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="24.09765625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="15.59765625" style="2" customWidth="1"/>
     <col min="15" max="15" width="18" style="2" customWidth="1"/>
-    <col min="16" max="16" width="10.625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="20.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.59765625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="20.09765625" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32" style="2" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
@@ -713,34 +1022,33 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
+      <c r="Q1" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" s="8" customFormat="1" ht="57">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="8" customFormat="1" ht="55.2">
       <c r="A2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",[1]!TabelaEquipamentos3[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
+        <v>34</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="F2" s="4">
         <v>162</v>
@@ -749,383 +1057,920 @@
         <v>1750</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="4"/>
+      <c r="O2" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="60.6" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" s="8" customFormat="1" ht="57">
-      <c r="A3" s="4" t="s">
+      <c r="D3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="3">
+        <v>165</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="55.2" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="3">
+        <v>118</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="12" customFormat="1" ht="55.2">
+      <c r="A5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="11">
+        <v>390</v>
+      </c>
+      <c r="G5" s="11">
+        <v>1750</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="55.2">
+      <c r="A6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="3">
+        <v>118</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="55.2">
+      <c r="A7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="3">
+        <v>118</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="N7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="55.2">
+      <c r="A8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="3">
+        <v>118</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",[1]!TabelaEquipamentos3[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="J8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="61.95" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="3">
+        <v>162</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="61.2" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="3">
+        <v>165</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="4">
+      <c r="N10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="61.2" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="3">
+        <v>165</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="12" customFormat="1" ht="61.2" customHeight="1">
+      <c r="A12" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="11">
+        <v>1750</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="61.2" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="3">
+        <v>118</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="61.2" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="3">
+        <v>118</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="12" customFormat="1" ht="61.95" customHeight="1">
+      <c r="A15" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15" s="11">
+        <v>390</v>
+      </c>
+      <c r="G15" s="11">
+        <v>1750</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="R15" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="61.2" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="3">
         <v>162</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G16" s="3">
         <v>1750</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="M16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="60" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="3">
+        <v>118</v>
+      </c>
+      <c r="G17" s="11">
+        <v>1750</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="I17" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4" t="s">
+      <c r="N17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="61.2" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="3">
+        <v>162</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="N18" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4" t="s">
+      <c r="O18" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="55.2">
+      <c r="A19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="24" customHeight="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="3">
+        <v>118</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
+      <c r="L19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>92</v>
+      </c>
       <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="Q19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1144,7 +1989,7 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:18">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1163,7 +2008,7 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:18">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1182,7 +2027,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:18">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1201,7 +2046,7 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:18">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1220,7 +2065,7 @@
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:18">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1239,7 +2084,7 @@
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:18">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1258,7 +2103,7 @@
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:18">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1277,7 +2122,7 @@
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:18">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1296,7 +2141,7 @@
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:18">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1315,7 +2160,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:18">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1334,7 +2179,7 @@
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:18">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1353,7 +2198,7 @@
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:18">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1962,132 +2807,62 @@
       <c r="Q63" s="3"/>
     </row>
     <row r="64" spans="1:17">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
+      <c r="A64" s="4"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="6"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
+      <c r="Q64" s="6"/>
     </row>
     <row r="65" spans="1:17">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="1:17">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="1:17">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="1:17">
-      <c r="A68" s="4"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="6"/>
-    </row>
-    <row r="69" spans="1:17">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="6"/>
+      <c r="Q65" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B70:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
+  <conditionalFormatting sqref="B67:B1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q19 Q3:Q8">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:R2">
+    <cfRule type="duplicateValues" dxfId="2" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R69">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  <conditionalFormatting sqref="R19:R65 R3:R8">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId1"/>
@@ -2100,90 +2875,90 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="66.125" customWidth="1"/>
+    <col min="1" max="1" width="66.09765625" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="9"/>
+    <row r="1" spans="1:2">
+      <c r="A1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="13"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
         <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/equipcaldeira1-INPASA.xlsx
+++ b/equipcaldeira1-INPASA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\PAGINAS WEB\DATABOOK_INPASA\CALDEIRA 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195BB12F-D7D2-4356-B3C0-C9A6CFE1EB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92D0416-C51D-4B0C-9EA4-494523DF3A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,9 +159,6 @@
     <t>RELATORIO FINAL</t>
   </si>
   <si>
-    <t>RE-401012</t>
-  </si>
-  <si>
     <t>C62344NA00GAW</t>
   </si>
   <si>
@@ -475,6 +472,9 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/img/vertimax.jpg</t>
+  </si>
+  <si>
+    <t>RE-401042A</t>
   </si>
 </sst>
 </file>
@@ -775,7 +775,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R65" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
-  <autoFilter ref="A1:R65" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+  <autoFilter ref="A1:R65" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="17">
+      <filters>
+        <filter val="OS 6341_x000a_TAG 7596361_x000a_TAG MOTOR 7597154_x000a_OS MOTOR"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="23"/>
     <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="22"/>
@@ -1028,27 +1034,27 @@
         <v>14</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" s="8" customFormat="1" ht="55.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="8" customFormat="1" ht="55.2" hidden="1">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F2" s="4">
         <v>162</v>
@@ -1063,44 +1069,44 @@
         <v>35</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
         <v>37</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>38</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="60.6" customHeight="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="60.6" hidden="1" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F3" s="3">
         <v>165</v>
@@ -1115,44 +1121,44 @@
         <v>35</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="55.2" customHeight="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="55.2" hidden="1" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F4" s="3">
         <v>118</v>
@@ -1167,44 +1173,44 @@
         <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="12" customFormat="1" ht="55.2">
       <c r="A5" s="11" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F5" s="11">
         <v>390</v>
@@ -1216,47 +1222,47 @@
         <v>36</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L5" s="11"/>
       <c r="M5" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="55.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="55.2" hidden="1">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F6" s="3">
         <v>118</v>
@@ -1271,44 +1277,44 @@
         <v>35</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="55.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="55.2" hidden="1">
       <c r="A7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F7" s="3">
         <v>118</v>
@@ -1323,44 +1329,44 @@
         <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="55.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="55.2" hidden="1">
       <c r="A8" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F8" s="3">
         <v>118</v>
@@ -1375,44 +1381,44 @@
         <v>35</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="61.95" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="61.95" hidden="1" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
         <v>162</v>
@@ -1427,44 +1433,44 @@
         <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
         <v>37</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N9" s="11" t="s">
         <v>38</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="61.2" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="61.2" hidden="1" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F10" s="3">
         <v>165</v>
@@ -1479,44 +1485,44 @@
         <v>35</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="61.2" customHeight="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="61.2" hidden="1" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F11" s="3">
         <v>165</v>
@@ -1531,47 +1537,47 @@
         <v>35</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" s="12" customFormat="1" ht="61.2" customHeight="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="12" customFormat="1" ht="61.2" hidden="1" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="G12" s="11">
         <v>1750</v>
@@ -1583,44 +1589,44 @@
         <v>35</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="61.2" hidden="1" customHeight="1">
+      <c r="A13" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="R12" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="61.2" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F13" s="3">
         <v>118</v>
@@ -1635,44 +1641,44 @@
         <v>35</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="61.2" hidden="1" customHeight="1">
+      <c r="A14" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="61.2" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F14" s="3">
         <v>118</v>
@@ -1691,40 +1697,40 @@
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" s="12" customFormat="1" ht="61.95" customHeight="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="12" customFormat="1" ht="61.95" hidden="1" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F15" s="11">
         <v>390</v>
@@ -1736,47 +1742,47 @@
         <v>36</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L15" s="11"/>
       <c r="M15" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="61.2" customHeight="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="61.2" hidden="1" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F16" s="3">
         <v>162</v>
@@ -1791,44 +1797,44 @@
         <v>35</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3" t="s">
         <v>37</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>38</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="60" hidden="1" customHeight="1">
+      <c r="A17" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="60" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F17" s="3">
         <v>118</v>
@@ -1843,44 +1849,44 @@
         <v>35</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="61.2" customHeight="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="61.2" hidden="1" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F18" s="3">
         <v>162</v>
@@ -1895,44 +1901,44 @@
         <v>35</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N18" s="10" t="s">
         <v>38</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="55.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="55.2" hidden="1">
       <c r="A19" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F19" s="3">
         <v>118</v>
@@ -1947,30 +1953,30 @@
         <v>35</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" hidden="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1989,7 +1995,7 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" hidden="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2008,7 +2014,7 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" hidden="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2027,7 +2033,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" hidden="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2046,7 +2052,7 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" hidden="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2065,7 +2071,7 @@
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" hidden="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2084,7 +2090,7 @@
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" hidden="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2103,7 +2109,7 @@
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" hidden="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -2122,7 +2128,7 @@
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" hidden="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2141,7 +2147,7 @@
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" hidden="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2160,7 +2166,7 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" hidden="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2179,7 +2185,7 @@
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" hidden="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2198,7 +2204,7 @@
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" hidden="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2217,7 +2223,7 @@
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" hidden="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2236,7 +2242,7 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" hidden="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2255,7 +2261,7 @@
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" hidden="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2274,7 +2280,7 @@
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" hidden="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2293,7 +2299,7 @@
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" hidden="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2312,7 +2318,7 @@
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" hidden="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2331,7 +2337,7 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" hidden="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2350,7 +2356,7 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" hidden="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2369,7 +2375,7 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" hidden="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2388,7 +2394,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" hidden="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2407,7 +2413,7 @@
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" hidden="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2426,7 +2432,7 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" hidden="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2445,7 +2451,7 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" hidden="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2464,7 +2470,7 @@
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" hidden="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2483,7 +2489,7 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" hidden="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2502,7 +2508,7 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" hidden="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2521,7 +2527,7 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" hidden="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2540,7 +2546,7 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" hidden="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2559,7 +2565,7 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" hidden="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2578,7 +2584,7 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" hidden="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2597,7 +2603,7 @@
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" hidden="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2616,7 +2622,7 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:17" hidden="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2635,7 +2641,7 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:17" hidden="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2654,7 +2660,7 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
     </row>
-    <row r="56" spans="1:17">
+    <row r="56" spans="1:17" hidden="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2673,7 +2679,7 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
     </row>
-    <row r="57" spans="1:17">
+    <row r="57" spans="1:17" hidden="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2692,7 +2698,7 @@
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
     </row>
-    <row r="58" spans="1:17">
+    <row r="58" spans="1:17" hidden="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2711,7 +2717,7 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
     </row>
-    <row r="59" spans="1:17">
+    <row r="59" spans="1:17" hidden="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -2730,7 +2736,7 @@
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
     </row>
-    <row r="60" spans="1:17">
+    <row r="60" spans="1:17" hidden="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -2749,7 +2755,7 @@
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
     </row>
-    <row r="61" spans="1:17">
+    <row r="61" spans="1:17" hidden="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2768,7 +2774,7 @@
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" hidden="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2787,7 +2793,7 @@
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:17" hidden="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -2806,7 +2812,7 @@
       <c r="P63" s="3"/>
       <c r="Q63" s="3"/>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:17" hidden="1">
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
       <c r="C64" s="6"/>
@@ -2825,7 +2831,7 @@
       <c r="P64" s="3"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:17">
+    <row r="65" spans="1:17" hidden="1">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>

--- a/equipcaldeira1-INPASA.xlsx
+++ b/equipcaldeira1-INPASA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\PAGINAS WEB\DATABOOK_INPASA\CALDEIRA 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92D0416-C51D-4B0C-9EA4-494523DF3A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B021C930-786D-4D09-8C91-1995498A743D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
